--- a/runs_eval/signal_controller_benchmark_real/full_performance_comparison_real.xlsx
+++ b/runs_eval/signal_controller_benchmark_real/full_performance_comparison_real.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Travid\updated_worst_case_MARL\runs_eval\signal_controller_benchmark_real\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF025D45-E83C-4A46-8A92-9F0DAAC23F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EDCA7C-FDFF-43E0-930F-DBBAF6BBE11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7404" yWindow="528" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1548,8 +1548,8 @@
         <v>15.68983333333331</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="8"/>
-        <v>-59.528050908562193</v>
+        <f>(C15-B15)/B15*100</f>
+        <v>-71.616854961965032</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="8"/>
@@ -1560,8 +1560,8 @@
         <v>7.0167174910646297</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="8"/>
-        <v>167.92209702184667</v>
+        <f>(F15-E15)/E15*100</f>
+        <v>154.55400318862755</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="8"/>
@@ -1572,8 +1572,8 @@
         <v>13.687196759259223</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="8"/>
-        <v>-42.579457149916351</v>
+        <f>(I15-H15)/H15*100</f>
+        <v>-29.254994195981354</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="8"/>
@@ -1584,8 +1584,8 @@
         <v>6.9225333854304596</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="8"/>
-        <v>20.622832751282399</v>
+        <f>(L15-K15)/K15*100</f>
+        <v>22.286974690798946</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" si="8"/>
@@ -1596,8 +1596,8 @@
         <v>26.26878472222219</v>
       </c>
       <c r="P15" s="1">
-        <f t="shared" si="8"/>
-        <v>-72.222845744368854</v>
+        <f>(O15-N15)/N15*100</f>
+        <v>-78.838339550020905</v>
       </c>
       <c r="Q15" s="1">
         <f t="shared" si="8"/>
@@ -1608,8 +1608,8 @@
         <v>5.9566178877791742</v>
       </c>
       <c r="S15" s="1">
-        <f t="shared" si="8"/>
-        <v>490.51762900169729</v>
+        <f>(R15-Q15)/Q15*100</f>
+        <v>219.16170461698817</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" si="8"/>
@@ -1620,8 +1620,8 @@
         <v>15.799145833333299</v>
       </c>
       <c r="V15" s="1">
-        <f t="shared" si="8"/>
-        <v>-68.970298112451488</v>
+        <f>(U15-T15)/T15*100</f>
+        <v>-75.44791646919245</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" si="8"/>
@@ -1632,8 +1632,8 @@
         <v>6.5501177067909042</v>
       </c>
       <c r="Y15" s="1">
-        <f t="shared" si="8"/>
-        <v>187.33804699277854</v>
+        <f>(X15-W15)/W15*100</f>
+        <v>161.7444772528236</v>
       </c>
     </row>
   </sheetData>

--- a/runs_eval/signal_controller_benchmark_real/full_performance_comparison_real.xlsx
+++ b/runs_eval/signal_controller_benchmark_real/full_performance_comparison_real.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Travid\updated_worst_case_MARL\runs_eval\signal_controller_benchmark_real\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EDCA7C-FDFF-43E0-930F-DBBAF6BBE11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453D295B-D11E-41E6-81CF-024554524ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="4188" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1544,7 +1544,7 @@
         <v>55.278699074073963</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" ref="C15:Y15" si="8">AVERAGE(C3:C14)</f>
+        <f t="shared" ref="C15:X15" si="8">AVERAGE(C3:C14)</f>
         <v>15.68983333333331</v>
       </c>
       <c r="D15" s="1">
